--- a/data/generated_v2/AB테스트_가상데이터_분석요약_v2.xlsx
+++ b/data/generated_v2/AB테스트_가상데이터_분석요약_v2.xlsx
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1352,7 +1352,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n"/>
+      <c r="A13" s="6" t="n"/>
       <c r="B13" s="7" t="n"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
@@ -1376,14 +1376,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>가설3: 유저 데이터 확보</t>
-        </is>
-      </c>
+      <c r="A14" s="6" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>반응입력 시작률</t>
+          <t>맞춤 추천 상품 CVR</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1393,17 +1389,17 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>18% x1.15 (가정(명시))</t>
+          <t>계획서 V1 신규: 초기 3.3%/목표 5% (참고치, 역산 목표 아님)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>22.73%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>select_item(reco)-&gt;동일세션 결제완료</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1413,12 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>18% (가정(명시), v1 승계)</t>
+          <t>계획서 V1 신규 (참고치)</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>17.16%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1435,7 +1431,7 @@
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>반응입력 완료율</t>
+          <t>추천 상품 화면 진입률</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1445,22 +1441,22 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>78% x1.15, cap 97% (가정(명시))</t>
+          <t>계획서 V1 신규: 초기 35~40%/목표 60% (참고치)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>89.34%</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>활성유저 기준, 90일 누적이라 목표 상회</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n"/>
+      <c r="A17" s="6" t="n"/>
       <c r="B17" s="7" t="n"/>
       <c r="C17" s="5" t="inlineStr">
         <is>
@@ -1469,30 +1465,193 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
+          <t>계획서 V1 신규 (참고치)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>89.53%</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>비교 기능 사용률</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>계획서 V1 개정(활성유저 기준): 초기 15~20%/목표 30~35% (참고치)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>54.78%</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>90일 누적이라 목표 상회</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>계획서 V1 개정 (참고치)</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>50.55%</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>가설3: 유저 데이터 확보</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>반응입력 시작률</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>18% x1.15 (가정(명시))</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>22.73%</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>18% (가정(명시), v1 승계)</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>17.16%</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>반응입력 완료율</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>78% x1.15, cap 97% (가정(명시))</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
           <t>78% (가정(명시), v1 승계)</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>75.86%</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
+    <mergeCell ref="A12:A19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B22:B23"/>
     <mergeCell ref="A2:A11"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A14:A17"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B20:B21"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="B14:B15"/>

--- a/data/generated_v2/AB테스트_가상데이터_분석요약_v2.xlsx
+++ b/data/generated_v2/AB테스트_가상데이터_분석요약_v2.xlsx
@@ -848,7 +848,7 @@
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>- 생성된 주문 수: A그룹 176건 / B그룹 169건</t>
+          <t>- 생성된 주문 수: A그룹 192건 / B그룹 189건</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  크게 줄었습니다(v2: A 176건 / B 169건). 이는 v1이 전환</t>
+          <t xml:space="preserve">  크게 줄었습니다(v2: A 192건 / B 189건). 이는 v1이 전환</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>3.57%</t>
+          <t>3.82%</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>33.59%</t>
+          <t>37.57%</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>34.14%</t>
+          <t>36.28%</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>66.41%</t>
+          <t>62.43%</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>65.86%</t>
+          <t>63.72%</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>49.2초</t>
+          <t>49.9초</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1.91일</t>
+          <t>2.21일</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2.84일</t>
+          <t>2.98일</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>28.6점</t>
+          <t>33.7점</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>21.0점</t>
+          <t>12.5점</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.36%</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>89.34%</t>
+          <t>89.05%</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>89.53%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>54.78%</t>
+          <t>54.66%</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>50.55%</t>
+          <t>51.21%</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>22.73%</t>
+          <t>17.19%</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>17.16%</t>
+          <t>20.11%</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>93.94%</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>75.86%</t>
+          <t>78.95%</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>13724</v>
+        <v>14079</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>13861</v>
+        <v>13622</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>100</v>
@@ -1747,22 +1747,22 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13720</v>
+        <v>14073</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>13854</v>
+        <v>13620</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>100</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>100</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4">
@@ -1772,22 +1772,22 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>495</v>
+        <v>521</v>
       </c>
       <c r="D4" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>3.8</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="F4" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="G4" s="5" t="n">
         <v>3.8</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>3.6</v>
       </c>
     </row>
     <row r="5">
@@ -1797,22 +1797,22 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>33.6</v>
+        <v>37.6</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>34.1</v>
+        <v>36.3</v>
       </c>
     </row>
   </sheetData>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>100</v>
@@ -1908,22 +1908,22 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>22.7</v>
+        <v>17.2</v>
       </c>
       <c r="E3" s="5" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F3" s="5" t="n">
         <v>17.2</v>
       </c>
-      <c r="F3" s="5" t="n">
-        <v>22.7</v>
-      </c>
       <c r="G3" s="5" t="n">
-        <v>17.2</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="4">
@@ -1933,16 +1933,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>22.7</v>
+        <v>17.2</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>17.2</v>
+        <v>20.1</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>100</v>
@@ -1958,22 +1958,22 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>18.2</v>
+        <v>16.1</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>13</v>
+        <v>15.9</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>80</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>75.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -1983,19 +1983,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>0</v>
@@ -2029,6 +2029,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2104,6 +2105,11 @@
           <t>11</t>
         </is>
       </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -2115,38 +2121,41 @@
         <v>0</v>
       </c>
       <c r="C3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="D3" s="5" t="n">
-        <v>1.3</v>
-      </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="J3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="K3" s="5" t="n">
+      <c r="L3" s="5" t="n">
         <v>1.3</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>0.6</v>
       </c>
       <c r="M3" s="5" t="n">
         <v>0.6</v>
       </c>
+      <c r="N3" s="5" t="n">
+        <v>2.6</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -2155,40 +2164,43 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="D4" s="5" t="n">
         <v>0.9</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0.9</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>0.4</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="L4" s="5" t="n">
         <v>0.4</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2198,16 +2210,16 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D5" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E5" s="5" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>1</v>
@@ -2216,21 +2228,24 @@
         <v>0.5</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2241,39 +2256,42 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0.9</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="H6" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I6" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="I6" s="5" t="n">
-        <v>1.9</v>
-      </c>
       <c r="J6" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K6" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="L6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2287,28 +2305,28 @@
         <v>0.5</v>
       </c>
       <c r="C7" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>1.1</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>0.5</v>
-      </c>
       <c r="E7" s="5" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="H7" s="5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I7" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" s="5" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
@@ -2317,6 +2335,9 @@
         <v>0</v>
       </c>
       <c r="M7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2333,7 +2354,7 @@
         <v>0.5</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>1</v>
@@ -2342,13 +2363,13 @@
         <v>1</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>1.9</v>
       </c>
-      <c r="H8" s="5" t="n">
-        <v>0.5</v>
-      </c>
       <c r="I8" s="5" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>0</v>
@@ -2360,6 +2381,9 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2370,25 +2394,25 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
@@ -2403,6 +2427,9 @@
         <v>0</v>
       </c>
       <c r="M9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2419,16 +2446,16 @@
         <v>1.1</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
@@ -2446,6 +2473,9 @@
         <v>0</v>
       </c>
       <c r="M10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2459,7 +2489,7 @@
         <v>0.7</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>2</v>
@@ -2468,7 +2498,7 @@
         <v>0.7</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0</v>
@@ -2489,6 +2519,9 @@
         <v>0</v>
       </c>
       <c r="M11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2499,16 +2532,16 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>1.6</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0</v>
@@ -2532,6 +2565,9 @@
         <v>0</v>
       </c>
       <c r="M12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2542,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>0</v>
@@ -2575,6 +2611,9 @@
         <v>0</v>
       </c>
       <c r="M13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2585,10 +2624,10 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>0</v>
@@ -2618,6 +2657,9 @@
         <v>0</v>
       </c>
       <c r="M14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2628,7 +2670,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>0</v>
@@ -2661,6 +2703,9 @@
         <v>0</v>
       </c>
       <c r="M15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2753,40 +2798,40 @@
         <v>0.6</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>1.2</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>1.2</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="I20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="J20" s="5" t="n">
-        <v>1.7</v>
-      </c>
       <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="L20" s="5" t="n">
-        <v>1.7</v>
-      </c>
       <c r="M20" s="5" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="21">
@@ -2796,40 +2841,40 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="C21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5" t="n">
         <v>1.1</v>
       </c>
-      <c r="D21" s="5" t="n">
-        <v>0.6</v>
-      </c>
       <c r="E21" s="5" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="G21" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H21" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="I21" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J21" s="5" t="n">
         <v>2.3</v>
       </c>
-      <c r="I21" s="5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K21" s="5" t="n">
-        <v>0.6</v>
+        <v>2.3</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="N21" s="5" t="n">
         <v>0</v>
@@ -2845,34 +2890,34 @@
         <v>0</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="M22" s="5" t="n">
         <v>0</v>
@@ -2888,34 +2933,34 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="C23" s="5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F23" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="G23" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K23" s="5" t="n">
         <v>1.6</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J23" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="L23" s="5" t="n">
         <v>0</v>
@@ -2940,25 +2985,25 @@
         <v>0.5</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="I24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>0.5</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>0</v>
@@ -2980,28 +3025,28 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>1.1</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G25" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>1.1</v>
       </c>
-      <c r="H25" s="5" t="n">
-        <v>0.5</v>
-      </c>
       <c r="I25" s="5" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J25" s="5" t="n">
         <v>0</v>
@@ -3029,22 +3074,22 @@
         <v>0</v>
       </c>
       <c r="C26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="F26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="5" t="n">
         <v>1.5</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>3</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>0</v>
@@ -3075,19 +3120,19 @@
         <v>0.5</v>
       </c>
       <c r="C27" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D27" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="D27" s="5" t="n">
-        <v>1.4</v>
-      </c>
       <c r="E27" s="5" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0</v>
@@ -3118,19 +3163,19 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C28" s="5" t="n">
         <v>1.1</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
@@ -3167,13 +3212,13 @@
         <v>0.5</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>0</v>
@@ -3210,10 +3255,10 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="D30" s="5" t="n">
         <v>1.1</v>
@@ -3259,7 +3304,7 @@
         <v>0.6</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>0</v>
@@ -3302,7 +3347,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="C32" s="5" t="n">
         <v>0</v>

--- a/data/generated_v2/AB테스트_가상데이터_분석요약_v2.xlsx
+++ b/data/generated_v2/AB테스트_가상데이터_분석요약_v2.xlsx
@@ -841,14 +841,14 @@
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>- 대상: A/B 각 2,500명 (총 5,000명), 90일간 순차 유입</t>
+          <t>- 대상: A/B 각 9,500명 (총 19,000명), 90일간 순차 유입</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>- 생성된 주문 수: A그룹 192건 / B그룹 189건</t>
+          <t>- 생성된 주문 수: A그룹 755건 / B그룹 587건</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
     <row r="22">
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  크게 줄었습니다(v2: A 192건 / B 189건). 이는 v1이 전환</t>
+          <t xml:space="preserve">  크게 줄었습니다(v2: A 755건 / B 587건). 이는 v1이 전환</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.91%</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>37.57%</t>
+          <t>36.92%</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>36.28%</t>
+          <t>31.27%</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>62.43%</t>
+          <t>63.08%</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>63.72%</t>
+          <t>68.73%</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>49.9초</t>
+          <t>49.6초</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>43.3초</t>
+          <t>43.0초</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>2.21일</t>
+          <t>2.14일</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>2.98일</t>
+          <t>2.29일</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>33.7점</t>
+          <t>33.1점</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>12.5점</t>
+          <t>24.1점</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>89.05%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.03%</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>54.66%</t>
+          <t>54.69%</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>51.21%</t>
+          <t>49.06%</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>17.19%</t>
+          <t>21.59%</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>20.11%</t>
+          <t>18.57%</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>93.94%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>78.95%</t>
+          <t>75.23%</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>14079</v>
+        <v>52339</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>13622</v>
+        <v>51731</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>100</v>
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>14073</v>
+        <v>52313</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>13620</v>
+        <v>51717</v>
       </c>
       <c r="D3" s="5" t="n">
         <v>100</v>
@@ -1772,22 +1772,22 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>511</v>
+        <v>2045</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>521</v>
+        <v>1877</v>
       </c>
       <c r="D4" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E4" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="E4" s="5" t="n">
-        <v>3.8</v>
-      </c>
       <c r="F4" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G4" s="5" t="n">
         <v>3.6</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>3.8</v>
       </c>
     </row>
     <row r="5">
@@ -1797,22 +1797,22 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>192</v>
+        <v>755</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>189</v>
+        <v>587</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>1.4</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>37.6</v>
+        <v>36.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>36.3</v>
+        <v>31.3</v>
       </c>
     </row>
   </sheetData>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>192</v>
+        <v>755</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>189</v>
+        <v>587</v>
       </c>
       <c r="D2" s="5" t="n">
         <v>100</v>
@@ -1908,22 +1908,22 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>33</v>
+        <v>163</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>17.2</v>
+        <v>21.6</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>20.1</v>
+        <v>18.6</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>17.2</v>
+        <v>21.6</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>20.1</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="4">
@@ -1933,16 +1933,16 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>33</v>
+        <v>163</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>17.2</v>
+        <v>21.6</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>20.1</v>
+        <v>18.6</v>
       </c>
       <c r="F4" s="5" t="n">
         <v>100</v>
@@ -1958,22 +1958,22 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>31</v>
+        <v>148</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>16.1</v>
+        <v>19.6</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>15.9</v>
+        <v>14</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>93.90000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>78.90000000000001</v>
+        <v>75.2</v>
       </c>
     </row>
     <row r="6">
@@ -1983,19 +1983,19 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>0</v>
@@ -2118,43 +2118,43 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="K3" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -2167,37 +2167,37 @@
         <v>0.4</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>2.6</v>
+        <v>0.8</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="N4" s="5" t="n">
         <v>0</v>
@@ -2210,37 +2210,37 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="M5" s="5" t="n">
         <v>0</v>
@@ -2256,34 +2256,34 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C6" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F6" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="G6" s="5" t="n">
-        <v>0.5</v>
-      </c>
       <c r="H6" s="5" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="L6" s="5" t="n">
         <v>0</v>
@@ -2302,31 +2302,31 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C7" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J7" s="5" t="n">
         <v>2.1</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>1.6</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
@@ -2348,28 +2348,28 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>0</v>
@@ -2394,25 +2394,25 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>0</v>
@@ -2440,22 +2440,22 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
@@ -2486,19 +2486,19 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="C11" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E11" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>2</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0.7</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0</v>
@@ -2532,16 +2532,16 @@
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>0</v>
@@ -2578,13 +2578,13 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>0</v>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>0</v>
@@ -2670,7 +2670,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>0</v>
@@ -2795,43 +2795,43 @@
         </is>
       </c>
       <c r="B20" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="C20" s="5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="F20" s="5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="G20" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I20" s="5" t="n">
         <v>0.6</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="M20" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="21">
@@ -2841,40 +2841,40 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.6</v>
+        <v>0.1</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>1.1</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="N21" s="5" t="n">
         <v>0</v>
@@ -2890,34 +2890,34 @@
         <v>0</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="M22" s="5" t="n">
         <v>0</v>
@@ -2933,31 +2933,31 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="E23" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G23" s="5" t="n">
         <v>1.1</v>
       </c>
-      <c r="F23" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>0.5</v>
-      </c>
       <c r="H23" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I23" s="5" t="n">
         <v>1.1</v>
       </c>
-      <c r="I23" s="5" t="n">
-        <v>2.1</v>
-      </c>
       <c r="J23" s="5" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>1.6</v>
@@ -2979,31 +2979,31 @@
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>0</v>
@@ -3025,28 +3025,28 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>1.1</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="J25" s="5" t="n">
         <v>0</v>
@@ -3071,25 +3071,25 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="I26" s="5" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0</v>
@@ -3163,19 +3163,19 @@
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
@@ -3212,13 +3212,13 @@
         <v>0.5</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="D29" s="5" t="n">
         <v>1.4</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>0</v>
@@ -3255,13 +3255,13 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="E30" s="5" t="n">
         <v>0</v>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>0</v>
@@ -3347,7 +3347,7 @@
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="C32" s="5" t="n">
         <v>0</v>

--- a/data/generated_v2/AB테스트_가상데이터_분석요약_v2.xlsx
+++ b/data/generated_v2/AB테스트_가상데이터_분석요약_v2.xlsx
@@ -9,9 +9,10 @@
   <sheets>
     <sheet name="개요" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="AB지표_비교" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="퍼널_구매여정" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="퍼널_반응입력여정" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="코호트_재구매율" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="판정결과" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="퍼널_구매여정" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="퍼널_반응입력여정" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="코호트_재구매율" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +52,23 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00555555"/>
       <sz val="9"/>
     </font>
     <font>
@@ -133,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,6 +165,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -808,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B30"/>
+  <dimension ref="B2:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="2" max="2"/>
@@ -983,21 +1004,28 @@
     <row r="28">
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2. 퍼널_구매여정 — 가설1 세션 단위 퍼널 (진입→탐색→장바구니→구매)</t>
+          <t>2. 판정결과 — 베이지안 P(A&gt;B) 기준 A/B 판정 (주 지표 3개 + 보조 지표 4개)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>3. 퍼널_반응입력여정 — 가설3 주문 단위 퍼널 (알람→확인→시작→완료→재진입)</t>
+          <t>3. 퍼널_구매여정 — 가설1 세션 단위 퍼널 (진입→탐색→장바구니→구매)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>4. 코호트_재구매율 — 가입 주차별 코호트의 주차별 구매 유저 비율(%)</t>
+          <t>4. 퍼널_반응입력여정 — 가설3 주문 단위 퍼널 (알람→확인→시작→완료→재진입)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>5. 코호트_재구매율 — 가입 주차별 코호트의 주차별 구매 유저 비율(%)</t>
         </is>
       </c>
     </row>
@@ -1666,6 +1694,434 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>판정 기준: 베이지안 사후확률 P(A&gt;B) &gt;= 90% (무정보 사전분포 Beta(1,1)) — 주 지표만 판정에 사용, 보조 지표는 방향 참고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>가설</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>지표</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>A (전환/모수)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>A 비율</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>B (전환/모수)</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>B 비율</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>P(A&gt;B)</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>주 지표</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>가설1: 선택 피로도 해소</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>구매전환율(진입 대비)</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>755/52339</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>587/51731</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>가설2: 서비스 충성도</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>맞춤 추천 재구매 CVR</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>397/23637</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>1.68%</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>288/23269</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>1.24%</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n"/>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>가설3: 유저 데이터 확보</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>반응 입력완료율(알람 대비)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>148/755</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>19.6%</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>82/587</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>13.97%</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>99.7%</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>보조 지표</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>가설1: 선택 피로도 해소</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>장바구니전환율(진입 대비)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>2045/52339</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>3.91%</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>1877/51731</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>3.63%</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>99.1%</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>방향 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>가설2: 서비스 충성도</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>NPS 추천자 비율</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>142/372</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>38.17%</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>89/291</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>30.58%</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>97.9%</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>방향 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>가설2: 서비스 충성도</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2회+ 구매 유저 비율(전체 유저)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>54/9500</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>0.57%</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>30/9500</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>0.32%</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>99.6%</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>방향 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>가설3: 유저 데이터 확보</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>알람 확인율</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>163/755</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>21.59%</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>109/587</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>18.57%</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>91.3%</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>방향 일치</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>※ 주의사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>- 지표를 여러 개 검정하면 그중 하나가 우연히 기준을 넘을 확률이 올라갑니다(90% 기준 7개 검정 시 최소 1건 거짓양성 확률 52%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  그래서 가설당 '주 지표' 1개만 판정에 사용하고, 보조 지표는 방향 참고로만 씁니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>- 가설3은 주 지표 표본(알람노출 주문)이 작아 효과크기 추정 구간이 넓습니다. 매출 임팩트 등 정량 계산에는 구간 하단을 보수적으로 쓰세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>- 자세한 판정 규칙과 근거는 docs/가설1_가설2_가설3_퍼널_분석_리포트.md 2.2~2.4절 참고.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1821,7 +2277,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2007,7 +2463,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2033,7 +2489,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>A그룹 — 가입 주차별 코호트 x 경과 주차별 구매 유저 비율(%)</t>
         </is>
@@ -2710,7 +3166,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>B그룹 — 가입 주차별 코호트 x 경과 주차별 구매 유저 비율(%)</t>
         </is>
